--- a/data/MK_ECB_DATA_20260708.xlsx
+++ b/data/MK_ECB_DATA_20260708.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E468"/>
+  <dimension ref="A1:E474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5908,25 +5908,25 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2.709578</v>
+        <v>2.51834</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2.713377</v>
+        <v>2.709578</v>
       </c>
     </row>
     <row r="241">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2.580816</v>
+        <v>2.713377</v>
       </c>
     </row>
     <row r="242">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>2.563197</v>
+        <v>2.580816</v>
       </c>
     </row>
     <row r="243">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2.590769</v>
+        <v>2.563197</v>
       </c>
     </row>
     <row r="244">
@@ -6037,11 +6037,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>2.651872</v>
+        <v>2.590769</v>
       </c>
     </row>
     <row r="245">
@@ -6060,11 +6060,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2.734067</v>
+        <v>2.651872</v>
       </c>
     </row>
     <row r="246">
@@ -6083,11 +6083,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>2.720401</v>
+        <v>2.734067</v>
       </c>
     </row>
     <row r="247">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>2.673633</v>
+        <v>2.720401</v>
       </c>
     </row>
     <row r="248">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>2.759799</v>
+        <v>2.673633</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>2.701019</v>
+        <v>2.759799</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2.758581</v>
+        <v>2.701019</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2.732917</v>
+        <v>2.758581</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2.690643</v>
+        <v>2.732917</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2.649058</v>
+        <v>2.690643</v>
       </c>
     </row>
     <row r="254">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2.550151</v>
+        <v>2.649058</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>2.600158</v>
+        <v>2.550151</v>
       </c>
     </row>
     <row r="256">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>2.584193</v>
+        <v>2.600158</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>2.60767</v>
+        <v>2.584193</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>2.573921</v>
+        <v>2.60767</v>
       </c>
     </row>
     <row r="259">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>2.664843</v>
+        <v>2.573921</v>
       </c>
     </row>
     <row r="260">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>2.631211</v>
+        <v>2.664843</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2.668913</v>
+        <v>2.631211</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2.667137</v>
+        <v>2.668913</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>2.690449</v>
+        <v>2.667137</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>2.70087</v>
+        <v>2.690449</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2.687806</v>
+        <v>2.70087</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2.718796</v>
+        <v>2.687806</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>2.687187</v>
+        <v>2.718796</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>2.661527</v>
+        <v>2.687187</v>
       </c>
     </row>
     <row r="269">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>2.585514</v>
+        <v>2.661527</v>
       </c>
     </row>
     <row r="270">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>2.586505</v>
+        <v>2.585514</v>
       </c>
     </row>
     <row r="271">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>2.599634</v>
+        <v>2.586505</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>2.625835</v>
+        <v>2.599634</v>
       </c>
     </row>
     <row r="273">
@@ -6704,11 +6704,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>2.653029</v>
+        <v>2.625835</v>
       </c>
     </row>
     <row r="274">
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2.611516</v>
+        <v>2.653029</v>
       </c>
     </row>
     <row r="275">
@@ -6750,11 +6750,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2.579206</v>
+        <v>2.611516</v>
       </c>
     </row>
     <row r="276">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>2.567358</v>
+        <v>2.579206</v>
       </c>
     </row>
     <row r="277">
@@ -6796,11 +6796,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>2.550469</v>
+        <v>2.567358</v>
       </c>
     </row>
     <row r="278">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>2.541062</v>
+        <v>2.550469</v>
       </c>
     </row>
     <row r="279">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>2.551573</v>
+        <v>2.541062</v>
       </c>
     </row>
     <row r="280">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>2.546422</v>
+        <v>2.551573</v>
       </c>
     </row>
     <row r="281">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>2.550091</v>
+        <v>2.546422</v>
       </c>
     </row>
     <row r="282">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>2.533759</v>
+        <v>2.550091</v>
       </c>
     </row>
     <row r="283">
@@ -6934,11 +6934,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>2.559161</v>
+        <v>2.533759</v>
       </c>
     </row>
     <row r="284">
@@ -6957,57 +6957,57 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2.55997</v>
+        <v>2.559161</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>2.785695</v>
+        <v>2.55997</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>2.791931</v>
+        <v>2.604448</v>
       </c>
     </row>
     <row r="287">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>2.660543</v>
+        <v>2.785695</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>2.647172</v>
+        <v>2.791931</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>2.668906</v>
+        <v>2.660543</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>2.727433</v>
+        <v>2.647172</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>2.812236</v>
+        <v>2.668906</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>2.800452</v>
+        <v>2.727433</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>2.746714</v>
+        <v>2.812236</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>2.846863</v>
+        <v>2.800452</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>2.787952</v>
+        <v>2.746714</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>2.854181</v>
+        <v>2.846863</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>2.823594</v>
+        <v>2.787952</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>2.775414</v>
+        <v>2.854181</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>2.73301</v>
+        <v>2.823594</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>2.632702</v>
+        <v>2.775414</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>2.685019</v>
+        <v>2.73301</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>2.665718</v>
+        <v>2.632702</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>2.685927</v>
+        <v>2.685019</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>2.653732</v>
+        <v>2.665718</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>2.737626</v>
+        <v>2.685927</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>2.695968</v>
+        <v>2.653732</v>
       </c>
     </row>
     <row r="307">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>2.739566</v>
+        <v>2.737626</v>
       </c>
     </row>
     <row r="308">
@@ -7509,11 +7509,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>2.742955</v>
+        <v>2.695968</v>
       </c>
     </row>
     <row r="309">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>2.76777</v>
+        <v>2.739566</v>
       </c>
     </row>
     <row r="310">
@@ -7555,11 +7555,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2.775779</v>
+        <v>2.742955</v>
       </c>
     </row>
     <row r="311">
@@ -7578,11 +7578,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2.765536</v>
+        <v>2.76777</v>
       </c>
     </row>
     <row r="312">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>2.79679</v>
+        <v>2.775779</v>
       </c>
     </row>
     <row r="313">
@@ -7624,11 +7624,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>2.759517</v>
+        <v>2.765536</v>
       </c>
     </row>
     <row r="314">
@@ -7647,11 +7647,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>2.740071</v>
+        <v>2.79679</v>
       </c>
     </row>
     <row r="315">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>2.664179</v>
+        <v>2.759517</v>
       </c>
     </row>
     <row r="316">
@@ -7693,11 +7693,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>2.660499</v>
+        <v>2.740071</v>
       </c>
     </row>
     <row r="317">
@@ -7716,11 +7716,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>2.66923</v>
+        <v>2.664179</v>
       </c>
     </row>
     <row r="318">
@@ -7739,11 +7739,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>2.694761</v>
+        <v>2.660499</v>
       </c>
     </row>
     <row r="319">
@@ -7762,11 +7762,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2.728076</v>
+        <v>2.66923</v>
       </c>
     </row>
     <row r="320">
@@ -7785,11 +7785,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>2.688614</v>
+        <v>2.694761</v>
       </c>
     </row>
     <row r="321">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>2.659069</v>
+        <v>2.728076</v>
       </c>
     </row>
     <row r="322">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>2.642481</v>
+        <v>2.688614</v>
       </c>
     </row>
     <row r="323">
@@ -7854,11 +7854,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>2.625755</v>
+        <v>2.659069</v>
       </c>
     </row>
     <row r="324">
@@ -7877,11 +7877,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>2.618788</v>
+        <v>2.642481</v>
       </c>
     </row>
     <row r="325">
@@ -7900,11 +7900,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2.629515</v>
+        <v>2.625755</v>
       </c>
     </row>
     <row r="326">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>2.625196</v>
+        <v>2.618788</v>
       </c>
     </row>
     <row r="327">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>2.637535</v>
+        <v>2.629515</v>
       </c>
     </row>
     <row r="328">
@@ -7969,11 +7969,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>2.62789</v>
+        <v>2.625196</v>
       </c>
     </row>
     <row r="329">
@@ -7992,11 +7992,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>2.65319</v>
+        <v>2.637535</v>
       </c>
     </row>
     <row r="330">
@@ -8015,80 +8015,80 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2.653312</v>
+        <v>2.62789</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>3.000517</v>
+        <v>2.65319</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>3.007991</v>
+        <v>2.653312</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2.886073</v>
+        <v>2.698194</v>
       </c>
     </row>
     <row r="334">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2.876206</v>
+        <v>3.000517</v>
       </c>
     </row>
     <row r="335">
@@ -8130,11 +8130,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2.889313</v>
+        <v>3.007991</v>
       </c>
     </row>
     <row r="336">
@@ -8153,11 +8153,11 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>2.939157</v>
+        <v>2.886073</v>
       </c>
     </row>
     <row r="337">
@@ -8176,11 +8176,11 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>3.015143</v>
+        <v>2.876206</v>
       </c>
     </row>
     <row r="338">
@@ -8199,11 +8199,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>3.012751</v>
+        <v>2.889313</v>
       </c>
     </row>
     <row r="339">
@@ -8222,11 +8222,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>2.955911</v>
+        <v>2.939157</v>
       </c>
     </row>
     <row r="340">
@@ -8245,11 +8245,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>3.063218</v>
+        <v>3.015143</v>
       </c>
     </row>
     <row r="341">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>3.014232</v>
+        <v>3.012751</v>
       </c>
     </row>
     <row r="342">
@@ -8291,11 +8291,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>3.077971</v>
+        <v>2.955911</v>
       </c>
     </row>
     <row r="343">
@@ -8314,11 +8314,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>3.044699</v>
+        <v>3.063218</v>
       </c>
     </row>
     <row r="344">
@@ -8337,11 +8337,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>2.995816</v>
+        <v>3.014232</v>
       </c>
     </row>
     <row r="345">
@@ -8360,11 +8360,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>2.948017</v>
+        <v>3.077971</v>
       </c>
     </row>
     <row r="346">
@@ -8383,11 +8383,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2.848562</v>
+        <v>3.044699</v>
       </c>
     </row>
     <row r="347">
@@ -8406,11 +8406,11 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2.900503</v>
+        <v>2.995816</v>
       </c>
     </row>
     <row r="348">
@@ -8429,11 +8429,11 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2.881685</v>
+        <v>2.948017</v>
       </c>
     </row>
     <row r="349">
@@ -8452,11 +8452,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2.899034</v>
+        <v>2.848562</v>
       </c>
     </row>
     <row r="350">
@@ -8475,11 +8475,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>2.869598</v>
+        <v>2.900503</v>
       </c>
     </row>
     <row r="351">
@@ -8498,11 +8498,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>2.942888</v>
+        <v>2.881685</v>
       </c>
     </row>
     <row r="352">
@@ -8521,11 +8521,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>2.892125</v>
+        <v>2.899034</v>
       </c>
     </row>
     <row r="353">
@@ -8544,11 +8544,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>2.936988</v>
+        <v>2.869598</v>
       </c>
     </row>
     <row r="354">
@@ -8567,11 +8567,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>2.946672</v>
+        <v>2.942888</v>
       </c>
     </row>
     <row r="355">
@@ -8590,11 +8590,11 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2.97218</v>
+        <v>2.892125</v>
       </c>
     </row>
     <row r="356">
@@ -8613,11 +8613,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>2.981788</v>
+        <v>2.936988</v>
       </c>
     </row>
     <row r="357">
@@ -8636,11 +8636,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>2.976278</v>
+        <v>2.946672</v>
       </c>
     </row>
     <row r="358">
@@ -8659,11 +8659,11 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>3.004347</v>
+        <v>2.97218</v>
       </c>
     </row>
     <row r="359">
@@ -8682,11 +8682,11 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>2.965561</v>
+        <v>2.981788</v>
       </c>
     </row>
     <row r="360">
@@ -8705,11 +8705,11 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>2.949891</v>
+        <v>2.976278</v>
       </c>
     </row>
     <row r="361">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2.878033</v>
+        <v>3.004347</v>
       </c>
     </row>
     <row r="362">
@@ -8751,11 +8751,11 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>2.866621</v>
+        <v>2.965561</v>
       </c>
     </row>
     <row r="363">
@@ -8774,11 +8774,11 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>2.868032</v>
+        <v>2.949891</v>
       </c>
     </row>
     <row r="364">
@@ -8797,11 +8797,11 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>2.886289</v>
+        <v>2.878033</v>
       </c>
     </row>
     <row r="365">
@@ -8820,11 +8820,11 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>2.926579</v>
+        <v>2.866621</v>
       </c>
     </row>
     <row r="366">
@@ -8843,11 +8843,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>2.892156</v>
+        <v>2.868032</v>
       </c>
     </row>
     <row r="367">
@@ -8866,11 +8866,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2.863126</v>
+        <v>2.886289</v>
       </c>
     </row>
     <row r="368">
@@ -8889,11 +8889,11 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>2.839867</v>
+        <v>2.926579</v>
       </c>
     </row>
     <row r="369">
@@ -8912,11 +8912,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>2.824154</v>
+        <v>2.892156</v>
       </c>
     </row>
     <row r="370">
@@ -8935,11 +8935,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>2.824752</v>
+        <v>2.863126</v>
       </c>
     </row>
     <row r="371">
@@ -8958,11 +8958,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>2.833752</v>
+        <v>2.839867</v>
       </c>
     </row>
     <row r="372">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>2.829627</v>
+        <v>2.824154</v>
       </c>
     </row>
     <row r="373">
@@ -9004,11 +9004,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>2.854952</v>
+        <v>2.824752</v>
       </c>
     </row>
     <row r="374">
@@ -9027,11 +9027,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>2.856888</v>
+        <v>2.833752</v>
       </c>
     </row>
     <row r="375">
@@ -9050,11 +9050,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>2.878062</v>
+        <v>2.829627</v>
       </c>
     </row>
     <row r="376">
@@ -9073,103 +9073,103 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>2.878889</v>
+        <v>2.854952</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>3.228543</v>
+        <v>2.856888</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>3.237712</v>
+        <v>2.878062</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>3.119151</v>
+        <v>2.878889</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>3.108997</v>
+        <v>2.920893</v>
       </c>
     </row>
     <row r="381">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>3.118124</v>
+        <v>3.228543</v>
       </c>
     </row>
     <row r="382">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>3.16475</v>
+        <v>3.237712</v>
       </c>
     </row>
     <row r="383">
@@ -9234,11 +9234,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>3.237417</v>
+        <v>3.119151</v>
       </c>
     </row>
     <row r="384">
@@ -9257,11 +9257,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>3.240594</v>
+        <v>3.108997</v>
       </c>
     </row>
     <row r="385">
@@ -9280,11 +9280,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>3.18189</v>
+        <v>3.118124</v>
       </c>
     </row>
     <row r="386">
@@ -9303,11 +9303,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>3.292831</v>
+        <v>3.16475</v>
       </c>
     </row>
     <row r="387">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>3.250782</v>
+        <v>3.237417</v>
       </c>
     </row>
     <row r="388">
@@ -9349,11 +9349,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>3.311581</v>
+        <v>3.240594</v>
       </c>
     </row>
     <row r="389">
@@ -9372,11 +9372,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>3.275978</v>
+        <v>3.18189</v>
       </c>
     </row>
     <row r="390">
@@ -9395,11 +9395,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>3.226414</v>
+        <v>3.292831</v>
       </c>
     </row>
     <row r="391">
@@ -9418,11 +9418,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>3.172951</v>
+        <v>3.250782</v>
       </c>
     </row>
     <row r="392">
@@ -9441,11 +9441,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>3.070373</v>
+        <v>3.311581</v>
       </c>
     </row>
     <row r="393">
@@ -9464,11 +9464,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>3.121809</v>
+        <v>3.275978</v>
       </c>
     </row>
     <row r="394">
@@ -9487,11 +9487,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>3.104055</v>
+        <v>3.226414</v>
       </c>
     </row>
     <row r="395">
@@ -9510,11 +9510,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>3.12121</v>
+        <v>3.172951</v>
       </c>
     </row>
     <row r="396">
@@ -9533,11 +9533,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>3.091758</v>
+        <v>3.070373</v>
       </c>
     </row>
     <row r="397">
@@ -9556,11 +9556,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>3.162397</v>
+        <v>3.121809</v>
       </c>
     </row>
     <row r="398">
@@ -9579,11 +9579,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>3.105972</v>
+        <v>3.104055</v>
       </c>
     </row>
     <row r="399">
@@ -9602,11 +9602,11 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>3.150735</v>
+        <v>3.12121</v>
       </c>
     </row>
     <row r="400">
@@ -9625,11 +9625,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>3.164004</v>
+        <v>3.091758</v>
       </c>
     </row>
     <row r="401">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>3.188864</v>
+        <v>3.162397</v>
       </c>
     </row>
     <row r="402">
@@ -9671,11 +9671,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>3.200686</v>
+        <v>3.105972</v>
       </c>
     </row>
     <row r="403">
@@ -9694,11 +9694,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>3.197992</v>
+        <v>3.150735</v>
       </c>
     </row>
     <row r="404">
@@ -9717,11 +9717,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>3.223329</v>
+        <v>3.164004</v>
       </c>
     </row>
     <row r="405">
@@ -9740,11 +9740,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>3.182662</v>
+        <v>3.188864</v>
       </c>
     </row>
     <row r="406">
@@ -9763,11 +9763,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>3.16864</v>
+        <v>3.200686</v>
       </c>
     </row>
     <row r="407">
@@ -9786,11 +9786,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>3.096218</v>
+        <v>3.197992</v>
       </c>
     </row>
     <row r="408">
@@ -9809,11 +9809,11 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>3.079783</v>
+        <v>3.223329</v>
       </c>
     </row>
     <row r="409">
@@ -9832,11 +9832,11 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>3.076564</v>
+        <v>3.182662</v>
       </c>
     </row>
     <row r="410">
@@ -9855,11 +9855,11 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>3.089147</v>
+        <v>3.16864</v>
       </c>
     </row>
     <row r="411">
@@ -9878,11 +9878,11 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>3.135827</v>
+        <v>3.096218</v>
       </c>
     </row>
     <row r="412">
@@ -9901,11 +9901,11 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>3.103015</v>
+        <v>3.079783</v>
       </c>
     </row>
     <row r="413">
@@ -9924,11 +9924,11 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>3.071323</v>
+        <v>3.076564</v>
       </c>
     </row>
     <row r="414">
@@ -9947,11 +9947,11 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>3.043622</v>
+        <v>3.089147</v>
       </c>
     </row>
     <row r="415">
@@ -9970,11 +9970,11 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>3.026814</v>
+        <v>3.135827</v>
       </c>
     </row>
     <row r="416">
@@ -9993,11 +9993,11 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>3.032928</v>
+        <v>3.103015</v>
       </c>
     </row>
     <row r="417">
@@ -10016,11 +10016,11 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>3.039436</v>
+        <v>3.071323</v>
       </c>
     </row>
     <row r="418">
@@ -10039,11 +10039,11 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>3.035337</v>
+        <v>3.043622</v>
       </c>
     </row>
     <row r="419">
@@ -10062,11 +10062,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>3.070159</v>
+        <v>3.026814</v>
       </c>
     </row>
     <row r="420">
@@ -10085,11 +10085,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>3.081383</v>
+        <v>3.032928</v>
       </c>
     </row>
     <row r="421">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>3.100713</v>
+        <v>3.039436</v>
       </c>
     </row>
     <row r="422">
@@ -10131,126 +10131,126 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>3.102715</v>
+        <v>3.035337</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>3.522383</v>
+        <v>3.070159</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>3.53446</v>
+        <v>3.081383</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>3.419526</v>
+        <v>3.100713</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>3.407866</v>
+        <v>3.102715</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>3.414486</v>
+        <v>3.143962</v>
       </c>
     </row>
     <row r="428">
@@ -10269,11 +10269,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>3.459084</v>
+        <v>3.522383</v>
       </c>
     </row>
     <row r="429">
@@ -10292,11 +10292,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>3.532267</v>
+        <v>3.53446</v>
       </c>
     </row>
     <row r="430">
@@ -10315,11 +10315,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>3.537955</v>
+        <v>3.419526</v>
       </c>
     </row>
     <row r="431">
@@ -10338,11 +10338,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>3.477861</v>
+        <v>3.407866</v>
       </c>
     </row>
     <row r="432">
@@ -10361,11 +10361,11 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>3.591227</v>
+        <v>3.414486</v>
       </c>
     </row>
     <row r="433">
@@ -10384,11 +10384,11 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>3.555828</v>
+        <v>3.459084</v>
       </c>
     </row>
     <row r="434">
@@ -10407,11 +10407,11 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>3.614122</v>
+        <v>3.532267</v>
       </c>
     </row>
     <row r="435">
@@ -10430,11 +10430,11 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>3.57531</v>
+        <v>3.537955</v>
       </c>
     </row>
     <row r="436">
@@ -10453,11 +10453,11 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>3.524301</v>
+        <v>3.477861</v>
       </c>
     </row>
     <row r="437">
@@ -10476,11 +10476,11 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>3.465361</v>
+        <v>3.591227</v>
       </c>
     </row>
     <row r="438">
@@ -10499,11 +10499,11 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>3.358616</v>
+        <v>3.555828</v>
       </c>
     </row>
     <row r="439">
@@ -10522,11 +10522,11 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>3.408954</v>
+        <v>3.614122</v>
       </c>
     </row>
     <row r="440">
@@ -10545,11 +10545,11 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>3.392661</v>
+        <v>3.57531</v>
       </c>
     </row>
     <row r="441">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>3.410886</v>
+        <v>3.524301</v>
       </c>
     </row>
     <row r="442">
@@ -10591,11 +10591,11 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>3.380955</v>
+        <v>3.465361</v>
       </c>
     </row>
     <row r="443">
@@ -10614,11 +10614,11 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E443" t="n">
-        <v>3.450091</v>
+        <v>3.358616</v>
       </c>
     </row>
     <row r="444">
@@ -10637,11 +10637,11 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>3.390251</v>
+        <v>3.408954</v>
       </c>
     </row>
     <row r="445">
@@ -10660,11 +10660,11 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E445" t="n">
-        <v>3.434872</v>
+        <v>3.392661</v>
       </c>
     </row>
     <row r="446">
@@ -10683,11 +10683,11 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>3.451103</v>
+        <v>3.410886</v>
       </c>
     </row>
     <row r="447">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>3.474414</v>
+        <v>3.380955</v>
       </c>
     </row>
     <row r="448">
@@ -10729,11 +10729,11 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>3.487726</v>
+        <v>3.450091</v>
       </c>
     </row>
     <row r="449">
@@ -10752,11 +10752,11 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>3.488064</v>
+        <v>3.390251</v>
       </c>
     </row>
     <row r="450">
@@ -10775,11 +10775,11 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>3.510348</v>
+        <v>3.434872</v>
       </c>
     </row>
     <row r="451">
@@ -10798,11 +10798,11 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>3.466867</v>
+        <v>3.451103</v>
       </c>
     </row>
     <row r="452">
@@ -10821,11 +10821,11 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>3.45513</v>
+        <v>3.474414</v>
       </c>
     </row>
     <row r="453">
@@ -10844,11 +10844,11 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>3.381408</v>
+        <v>3.487726</v>
       </c>
     </row>
     <row r="454">
@@ -10867,11 +10867,11 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>3.360241</v>
+        <v>3.488064</v>
       </c>
     </row>
     <row r="455">
@@ -10890,11 +10890,11 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>3.35235</v>
+        <v>3.510348</v>
       </c>
     </row>
     <row r="456">
@@ -10913,11 +10913,11 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>3.358799</v>
+        <v>3.466867</v>
       </c>
     </row>
     <row r="457">
@@ -10936,11 +10936,11 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>3.413209</v>
+        <v>3.45513</v>
       </c>
     </row>
     <row r="458">
@@ -10959,11 +10959,11 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>3.381184</v>
+        <v>3.381408</v>
       </c>
     </row>
     <row r="459">
@@ -10982,11 +10982,11 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>3.34561</v>
+        <v>3.360241</v>
       </c>
     </row>
     <row r="460">
@@ -11005,11 +11005,11 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>3.313304</v>
+        <v>3.35235</v>
       </c>
     </row>
     <row r="461">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>3.294135</v>
+        <v>3.358799</v>
       </c>
     </row>
     <row r="462">
@@ -11051,11 +11051,11 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>3.306326</v>
+        <v>3.413209</v>
       </c>
     </row>
     <row r="463">
@@ -11074,11 +11074,11 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>3.309678</v>
+        <v>3.381184</v>
       </c>
     </row>
     <row r="464">
@@ -11097,11 +11097,11 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>3.306024</v>
+        <v>3.34561</v>
       </c>
     </row>
     <row r="465">
@@ -11120,11 +11120,11 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>3.350751</v>
+        <v>3.313304</v>
       </c>
     </row>
     <row r="466">
@@ -11143,11 +11143,11 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>3.371501</v>
+        <v>3.294135</v>
       </c>
     </row>
     <row r="467">
@@ -11166,11 +11166,11 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>3.39017</v>
+        <v>3.306326</v>
       </c>
     </row>
     <row r="468">
@@ -11189,11 +11189,149 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>3.309678</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>10</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>3.306024</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>10</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>3.350751</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>10</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>3.371501</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>10</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>20260703</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>3.39017</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>10</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
           <t>20260706</t>
         </is>
       </c>
-      <c r="E468" t="n">
+      <c r="E473" t="n">
         <v>3.393866</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>10</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>3.435339</v>
       </c>
     </row>
   </sheetData>
